--- a/diseases/d019/2005-2009.xlsx
+++ b/diseases/d019/2005-2009.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1309,9 +1306,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1605,9 +1599,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -1901,9 +1892,6 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -2197,9 +2185,6 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -2493,9 +2478,6 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
@@ -2789,9 +2771,6 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -3085,9 +3064,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -3381,9 +3357,6 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -3677,9 +3650,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -3973,9 +3943,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -4269,9 +4236,6 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -4565,9 +4529,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -4861,9 +4822,6 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -5257,9 +5215,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -5553,9 +5508,6 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
@@ -5849,9 +5801,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -6145,9 +6094,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -6441,9 +6387,6 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
@@ -6737,9 +6680,6 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
@@ -7033,9 +6973,6 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -7329,9 +7266,6 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
@@ -7625,9 +7559,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -7921,9 +7852,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -8217,9 +8145,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -8513,9 +8438,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -8957,9 +8879,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -9353,9 +9272,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -9797,9 +9713,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -10241,9 +10154,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -10685,9 +10595,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -11129,9 +11036,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -11573,9 +11477,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -12017,9 +11918,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -12461,9 +12359,6 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -12905,9 +12800,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -13349,9 +13241,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -13793,9 +13682,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -14237,9 +14123,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -14681,9 +14564,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -15077,9 +14957,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -15521,9 +15398,6 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
@@ -15965,9 +15839,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
@@ -16409,9 +16280,6 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
@@ -16853,9 +16721,6 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
@@ -17297,9 +17162,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -17741,9 +17603,6 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
@@ -18185,9 +18044,6 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -18629,9 +18485,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -19073,9 +18926,6 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
@@ -19517,9 +19367,6 @@
       <c r="O126" t="n">
         <v>0</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0</v>
       </c>
@@ -19961,9 +19808,6 @@
       <c r="O129" t="n">
         <v>0</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0</v>
       </c>
@@ -20405,9 +20249,6 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
@@ -20801,9 +20642,6 @@
       <c r="O134" t="n">
         <v>0</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0</v>
       </c>
@@ -21245,9 +21083,6 @@
       <c r="O137" t="n">
         <v>0</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0</v>
       </c>
@@ -21689,9 +21524,6 @@
       <c r="O140" t="n">
         <v>0</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0</v>
       </c>
@@ -22133,9 +21965,6 @@
       <c r="O143" t="n">
         <v>0</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0</v>
       </c>
@@ -22577,9 +22406,6 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
@@ -23021,9 +22847,6 @@
       <c r="O149" t="n">
         <v>0</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0</v>
       </c>
@@ -23465,9 +23288,6 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0</v>
       </c>
@@ -23909,9 +23729,6 @@
       <c r="O155" t="n">
         <v>0</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0</v>
       </c>
@@ -24353,9 +24170,6 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0</v>
       </c>
@@ -24797,9 +24611,6 @@
       <c r="O161" t="n">
         <v>0</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0</v>
       </c>
@@ -25241,9 +25052,6 @@
       <c r="O164" t="n">
         <v>0</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0</v>
       </c>
@@ -25683,9 +25491,6 @@
         <v>0</v>
       </c>
       <c r="O167" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q167" t="n">
         <v>0</v>
       </c>
       <c r="R167" t="n">
